--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.104827448472377</v>
+        <v>0.5045344603767613</v>
       </c>
       <c r="D2" t="n">
-        <v>2.456668426665297</v>
+        <v>0.3992086193331107</v>
       </c>
       <c r="E2" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F2" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.8149539389518</v>
+        <v>2.894930015079667</v>
       </c>
       <c r="D3" t="n">
-        <v>17.35564676382686</v>
+        <v>2.820292599121865</v>
       </c>
       <c r="E3" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F3" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.706744235583991</v>
+        <v>0.9273459382823985</v>
       </c>
       <c r="D4" t="n">
-        <v>6.002480352242646</v>
+        <v>0.97540305723943</v>
       </c>
       <c r="E4" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F4" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.37482615505117</v>
+        <v>2.985909250195815</v>
       </c>
       <c r="D5" t="n">
-        <v>18.80228878291933</v>
+        <v>3.055371927224392</v>
       </c>
       <c r="E5" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F5" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.212574785299759</v>
+        <v>0.8470434026112108</v>
       </c>
       <c r="D6" t="n">
-        <v>5.387473017877232</v>
+        <v>0.8754643654050502</v>
       </c>
       <c r="E6" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F6" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.28036532437452</v>
+        <v>0.3705593652108595</v>
       </c>
       <c r="D7" t="n">
-        <v>1.676368099712126</v>
+        <v>0.2724098162032206</v>
       </c>
       <c r="E7" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F7" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.9555296783217</v>
+        <v>1.617773572727276</v>
       </c>
       <c r="D8" t="n">
-        <v>12.08837421580781</v>
+        <v>1.96436081006877</v>
       </c>
       <c r="E8" t="n">
-        <v>6.228474313213282</v>
+        <v>1.012127075897159</v>
       </c>
       <c r="F8" t="n">
-        <v>6.478993033005899</v>
+        <v>1.052836367863459</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
